--- a/ZOI-SL-IL-5100/D5. File Aksesoris ZOI-SL-IL-5100.xlsx
+++ b/ZOI-SL-IL-5100/D5. File Aksesoris ZOI-SL-IL-5100.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27928"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\R&amp;D PT. Cahaya Hasil Cemerlang Multi Manufaktur\PERSIAPAN IZIN EDAR\SURGICAL LIGHT\1. ZOI-SL-IL-5100 ZOI Ilios 5000 Series Surgical Light - Single Dome\DOKUMEN TEKNIS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fb713085e485f505/Desktop/IZIN EDAR SURGICAL LIGHT TERBARU/ZOI-SL-IL-5100/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFD75F87-3838-4F11-B78F-34EEFA830AEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{EFD75F87-3838-4F11-B78F-34EEFA830AEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F1F49D4D-6D5C-44D6-9D02-9F1F7E7DAC87}"/>
   <bookViews>
-    <workbookView xWindow="3165" yWindow="855" windowWidth="15825" windowHeight="14625" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Aksesoris" sheetId="1" r:id="rId1"/>
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -199,7 +199,9 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9"/>
+  <tableStyles count="1" defaultTableStyle="TableStyleMedium9">
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{EB0D63A2-705E-4007-A0B1-6212C547E0A7}"/>
+  </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
